--- a/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.22.xlsx
+++ b/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.22.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="oocihm.22250.22" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="oocihm.22250.22" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -581,12 +581,12 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.22.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.22.txt</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0022.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0022.txt</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr"/>
@@ -843,7 +843,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">

--- a/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.22.xlsx
+++ b/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.22.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="oocihm.22250.22" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="oocihm.22250.22" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -422,18 +422,18 @@
     <col width="39" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="33" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="36" customWidth="1" min="6" max="6"/>
     <col width="35" customWidth="1" min="7" max="7"/>
     <col width="60" customWidth="1" min="8" max="8"/>
     <col width="60" customWidth="1" min="9" max="9"/>
-    <col width="60" customWidth="1" min="10" max="10"/>
+    <col width="27" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
     <col width="49" customWidth="1" min="14" max="14"/>
-    <col width="49" customWidth="1" min="15" max="15"/>
+    <col width="60" customWidth="1" min="15" max="15"/>
     <col width="31" customWidth="1" min="16" max="16"/>
     <col width="60" customWidth="1" min="17" max="17"/>
     <col width="30" customWidth="1" min="18" max="18"/>
@@ -603,18 +603,18 @@
           <t>L7: line starts with digit/letter garbage token | suspicious token(s): 1er (letter/digit mix) :: 1er or ex-</t>
         </is>
       </c>
-      <c r="J2" s="1" t="inlineStr">
-        <is>
-          <t>L101: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: registry, and sign the same â€œRegistered this of</t>
-        </is>
-      </c>
+      <c r="J2" s="1" t="inlineStr"/>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L50: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+02DC SMALL TILDE :: said, a certificate whereof shall be duly registered, shall beâ€˜</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]15</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]15</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
           <t>L2: isolated marker/symbol line :: 15</t>
@@ -622,13 +622,13 @@
       </c>
       <c r="O2" s="1" t="inlineStr">
         <is>
-          <t>L42: isolated marker/symbol line :: :</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]15</t>
         </is>
       </c>
       <c r="P2" s="1" t="inlineStr"/>
       <c r="Q2" s="1" t="inlineStr">
         <is>
-          <t>L86: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: double/multiple hyphen :: â€” --------A. D. eighteen, ------------------------------already regis-</t>
+          <t>L54: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | punctuation artifact: hyphen/bullet debris :: of such deed or conveyance shall have been duly regis-•</t>
         </is>
       </c>
       <c r="R2" s="1" t="inlineStr"/>
@@ -657,7 +657,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>94</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr"/>
@@ -673,7 +673,7 @@
       <c r="J3" s="1" t="inlineStr"/>
       <c r="K3" s="1" t="inlineStr">
         <is>
-          <t>L54: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: of such deed or conveyance shall have been duly regis-â€¢</t>
+          <t>L54: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | punctuation artifact: hyphen/bullet debris :: of such deed or conveyance shall have been duly regis-•</t>
         </is>
       </c>
       <c r="L3" s="1" t="inlineStr"/>
@@ -685,11 +685,15 @@
       </c>
       <c r="O3" s="1" t="inlineStr">
         <is>
-          <t>L104: symbol-only separator/garbage line :: 34.</t>
+          <t>L42: isolated marker/symbol line :: :</t>
         </is>
       </c>
       <c r="P3" s="1" t="inlineStr"/>
-      <c r="Q3" s="1" t="inlineStr"/>
+      <c r="Q3" s="1" t="inlineStr">
+        <is>
+          <t>L86: punctuation artifact: double/multiple hyphen :: — --------A. D. eighteen, ------------------------------already regis-</t>
+        </is>
+      </c>
       <c r="R3" s="1" t="inlineStr"/>
       <c r="S3" s="1" t="inlineStr"/>
       <c r="T3" s="1" t="inlineStr"/>
@@ -722,11 +726,7 @@
       <c r="H4" s="1" t="inlineStr"/>
       <c r="I4" s="1" t="inlineStr"/>
       <c r="J4" s="1" t="inlineStr"/>
-      <c r="K4" s="1" t="inlineStr">
-        <is>
-          <t>L85: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: registry, and sign the same" Registered thisâ€” day of judgments</t>
-        </is>
-      </c>
+      <c r="K4" s="1" t="inlineStr"/>
       <c r="L4" s="1" t="inlineStr"/>
       <c r="M4" s="1" t="inlineStr"/>
       <c r="N4" s="1" t="inlineStr">
@@ -736,7 +736,7 @@
       </c>
       <c r="O4" s="1" t="inlineStr">
         <is>
-          <t>L106: isolated marker/symbol line :: 7</t>
+          <t>L104: symbol-only separator/garbage line :: 34.</t>
         </is>
       </c>
       <c r="P4" s="1" t="inlineStr"/>
@@ -758,12 +758,12 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr"/>
@@ -773,11 +773,7 @@
       <c r="H5" s="1" t="inlineStr"/>
       <c r="I5" s="1" t="inlineStr"/>
       <c r="J5" s="1" t="inlineStr"/>
-      <c r="K5" s="1" t="inlineStr">
-        <is>
-          <t>L86: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: double/multiple hyphen :: â€” --------A. D. eighteen, ------------------------------already regis-</t>
-        </is>
-      </c>
+      <c r="K5" s="1" t="inlineStr"/>
       <c r="L5" s="1" t="inlineStr"/>
       <c r="M5" s="1" t="inlineStr"/>
       <c r="N5" s="1" t="inlineStr">
@@ -785,7 +781,11 @@
           <t>L103: symbol-only separator/garbage line :: 34.</t>
         </is>
       </c>
-      <c r="O5" s="1" t="inlineStr"/>
+      <c r="O5" s="1" t="inlineStr">
+        <is>
+          <t>L106: isolated marker/symbol line :: 7</t>
+        </is>
+      </c>
       <c r="P5" s="1" t="inlineStr"/>
       <c r="Q5" s="1" t="inlineStr"/>
       <c r="R5" s="1" t="inlineStr"/>
@@ -969,12 +969,12 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr"/>
@@ -1013,7 +1013,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
@@ -1052,7 +1052,7 @@
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D12" s="1" t="inlineStr"/>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="C13" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D13" s="1" t="inlineStr"/>
